--- a/docs/打字練習.xlsx
+++ b/docs/打字練習.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739E70E1-44F8-40D8-8A27-F55BF57F88E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03498549-9F37-45A3-A721-BA9FEBF8CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" xr2:uid="{E1B05DE5-EAD7-43D6-8DFE-DCA2C8EA1D01}"/>
+    <workbookView xWindow="67080" yWindow="-105" windowWidth="16440" windowHeight="28320" xr2:uid="{E1B05DE5-EAD7-43D6-8DFE-DCA2C8EA1D01}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="打字練習表" sheetId="1" r:id="rId1"/>
     <sheet name="音調表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -812,18 +812,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -846,6 +834,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,103 +1204,103 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="3" spans="2:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="14">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="10">
         <v>1</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="11">
         <v>2</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="11">
         <v>3</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="11">
         <v>4</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="11">
         <v>5</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="11">
         <v>6</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="11">
         <v>7</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="11">
         <v>8</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="15">
         <f>IF( LEN(C4)&gt;0, LEN(C4), "")</f>
         <v>6</v>
       </c>
-      <c r="E4" s="20" t="str" cm="1">
+      <c r="E4" s="16" t="str" cm="1">
         <f t="array" ref="E4" xml:space="preserve"> IF(E$3&lt;&gt;$D4, MID($C4,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>l</v>
       </c>
-      <c r="F4" s="20" t="str" cm="1">
+      <c r="F4" s="16" t="str" cm="1">
         <f t="array" ref="F4" xml:space="preserve"> IF(F$3&lt;&gt;$D4, MID($C4,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G4" s="20" t="str" cm="1">
+      <c r="G4" s="16" t="str" cm="1">
         <f t="array" ref="G4" xml:space="preserve"> IF(G$3&lt;&gt;$D4, MID($C4,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H4" s="20" t="str" cm="1">
+      <c r="H4" s="16" t="str" cm="1">
         <f t="array" ref="H4" xml:space="preserve"> IF(H$3&lt;&gt;$D4, MID($C4,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I4" s="20" t="str" cm="1">
+      <c r="I4" s="16" t="str" cm="1">
         <f t="array" ref="I4" xml:space="preserve"> IF(I$3&lt;&gt;$D4, MID($C4,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J4" s="20" t="str" cm="1">
+      <c r="J4" s="16" t="str" cm="1">
         <f t="array" ref="J4" xml:space="preserve"> IF(J$3&lt;&gt;$D4, MID($C4,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="K4" s="20" t="str" cm="1">
+      <c r="K4" s="16" t="str" cm="1">
         <f t="array" ref="K4" xml:space="preserve"> IF(K$3&lt;&gt;$D4, MID($C4,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L4" s="20" t="str" cm="1">
+      <c r="L4" s="16" t="str" cm="1">
         <f t="array" ref="L4" xml:space="preserve"> IF(L$3&lt;&gt;$D4, MID($C4,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M4" s="21" t="str" cm="1">
+      <c r="M4" s="17" t="str" cm="1">
         <f t="array" ref="M4" xml:space="preserve"> IF(M$3&lt;&gt;$D4, MID($C4,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C4,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1312,49 +1312,49 @@
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="15">
         <f t="shared" ref="D5:D44" si="0">IF( LEN(C5)&gt;0, LEN(C5), "")</f>
         <v>4</v>
       </c>
-      <c r="E5" s="20" t="str" cm="1">
+      <c r="E5" s="16" t="str" cm="1">
         <f t="array" ref="E5" xml:space="preserve"> IF(E$3&lt;&gt;$D5, MID($C5,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>z</v>
       </c>
-      <c r="F5" s="20" t="str" cm="1">
+      <c r="F5" s="16" t="str" cm="1">
         <f t="array" ref="F5" xml:space="preserve"> IF(F$3&lt;&gt;$D5, MID($C5,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G5" s="20" t="str" cm="1">
+      <c r="G5" s="16" t="str" cm="1">
         <f t="array" ref="G5" xml:space="preserve"> IF(G$3&lt;&gt;$D5, MID($C5,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H5" s="20" t="str" cm="1">
+      <c r="H5" s="16" t="str" cm="1">
         <f t="array" ref="H5" xml:space="preserve"> IF(H$3&lt;&gt;$D5, MID($C5,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="I5" s="20" t="str" cm="1">
+      <c r="I5" s="16" t="str" cm="1">
         <f t="array" ref="I5" xml:space="preserve"> IF(I$3&lt;&gt;$D5, MID($C5,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J5" s="20" t="str" cm="1">
+      <c r="J5" s="16" t="str" cm="1">
         <f t="array" ref="J5" xml:space="preserve"> IF(J$3&lt;&gt;$D5, MID($C5,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K5" s="20" t="str" cm="1">
+      <c r="K5" s="16" t="str" cm="1">
         <f t="array" ref="K5" xml:space="preserve"> IF(K$3&lt;&gt;$D5, MID($C5,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L5" s="20" t="str" cm="1">
+      <c r="L5" s="16" t="str" cm="1">
         <f t="array" ref="L5" xml:space="preserve"> IF(L$3&lt;&gt;$D5, MID($C5,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M5" s="21" t="str" cm="1">
+      <c r="M5" s="17" t="str" cm="1">
         <f t="array" ref="M5" xml:space="preserve"> IF(M$3&lt;&gt;$D5, MID($C5,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C5,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1362,49 +1362,49 @@
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E6" s="20" t="str" cm="1">
+      <c r="E6" s="16" t="str" cm="1">
         <f t="array" ref="E6" xml:space="preserve"> IF(E$3&lt;&gt;$D6, MID($C6,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="F6" s="20" t="str" cm="1">
+      <c r="F6" s="16" t="str" cm="1">
         <f t="array" ref="F6" xml:space="preserve"> IF(F$3&lt;&gt;$D6, MID($C6,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G6" s="20" t="str" cm="1">
+      <c r="G6" s="16" t="str" cm="1">
         <f t="array" ref="G6" xml:space="preserve"> IF(G$3&lt;&gt;$D6, MID($C6,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="H6" s="20" t="str" cm="1">
+      <c r="H6" s="16" t="str" cm="1">
         <f t="array" ref="H6" xml:space="preserve"> IF(H$3&lt;&gt;$D6, MID($C6,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I6" s="20" t="str" cm="1">
+      <c r="I6" s="16" t="str" cm="1">
         <f t="array" ref="I6" xml:space="preserve"> IF(I$3&lt;&gt;$D6, MID($C6,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J6" s="20" t="str" cm="1">
+      <c r="J6" s="16" t="str" cm="1">
         <f t="array" ref="J6" xml:space="preserve"> IF(J$3&lt;&gt;$D6, MID($C6,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K6" s="20" t="str" cm="1">
+      <c r="K6" s="16" t="str" cm="1">
         <f t="array" ref="K6" xml:space="preserve"> IF(K$3&lt;&gt;$D6, MID($C6,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L6" s="20" t="str" cm="1">
+      <c r="L6" s="16" t="str" cm="1">
         <f t="array" ref="L6" xml:space="preserve"> IF(L$3&lt;&gt;$D6, MID($C6,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M6" s="21" t="str" cm="1">
+      <c r="M6" s="17" t="str" cm="1">
         <f t="array" ref="M6" xml:space="preserve"> IF(M$3&lt;&gt;$D6, MID($C6,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C6,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1412,45 +1412,45 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="20" t="str" cm="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="16" t="str" cm="1">
         <f t="array" ref="E7" xml:space="preserve"> IF(E$3&lt;&gt;$D7, MID($C7,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="F7" s="20" t="str" cm="1">
+      <c r="F7" s="16" t="str" cm="1">
         <f t="array" ref="F7" xml:space="preserve"> IF(F$3&lt;&gt;$D7, MID($C7,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G7" s="20" t="str" cm="1">
+      <c r="G7" s="16" t="str" cm="1">
         <f t="array" ref="G7" xml:space="preserve"> IF(G$3&lt;&gt;$D7, MID($C7,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H7" s="20" t="str" cm="1">
+      <c r="H7" s="16" t="str" cm="1">
         <f t="array" ref="H7" xml:space="preserve"> IF(H$3&lt;&gt;$D7, MID($C7,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I7" s="20" t="str" cm="1">
+      <c r="I7" s="16" t="str" cm="1">
         <f t="array" ref="I7" xml:space="preserve"> IF(I$3&lt;&gt;$D7, MID($C7,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J7" s="20" t="str" cm="1">
+      <c r="J7" s="16" t="str" cm="1">
         <f t="array" ref="J7" xml:space="preserve"> IF(J$3&lt;&gt;$D7, MID($C7,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K7" s="20" t="str" cm="1">
+      <c r="K7" s="16" t="str" cm="1">
         <f t="array" ref="K7" xml:space="preserve"> IF(K$3&lt;&gt;$D7, MID($C7,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L7" s="20" t="str" cm="1">
+      <c r="L7" s="16" t="str" cm="1">
         <f t="array" ref="L7" xml:space="preserve"> IF(L$3&lt;&gt;$D7, MID($C7,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M7" s="21" t="str" cm="1">
+      <c r="M7" s="17" t="str" cm="1">
         <f t="array" ref="M7" xml:space="preserve"> IF(M$3&lt;&gt;$D7, MID($C7,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C7,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1458,49 +1458,49 @@
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E8" s="20" t="str" cm="1">
+      <c r="E8" s="16" t="str" cm="1">
         <f t="array" ref="E8" xml:space="preserve"> IF(E$3&lt;&gt;$D8, MID($C8,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="F8" s="20" t="str" cm="1">
+      <c r="F8" s="16" t="str" cm="1">
         <f t="array" ref="F8" xml:space="preserve"> IF(F$3&lt;&gt;$D8, MID($C8,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="G8" s="20" t="str" cm="1">
+      <c r="G8" s="16" t="str" cm="1">
         <f t="array" ref="G8" xml:space="preserve"> IF(G$3&lt;&gt;$D8, MID($C8,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="H8" s="20" t="str" cm="1">
+      <c r="H8" s="16" t="str" cm="1">
         <f t="array" ref="H8" xml:space="preserve"> IF(H$3&lt;&gt;$D8, MID($C8,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="I8" s="20" t="str" cm="1">
+      <c r="I8" s="16" t="str" cm="1">
         <f t="array" ref="I8" xml:space="preserve"> IF(I$3&lt;&gt;$D8, MID($C8,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J8" s="20" t="str" cm="1">
+      <c r="J8" s="16" t="str" cm="1">
         <f t="array" ref="J8" xml:space="preserve"> IF(J$3&lt;&gt;$D8, MID($C8,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K8" s="20" t="str" cm="1">
+      <c r="K8" s="16" t="str" cm="1">
         <f t="array" ref="K8" xml:space="preserve"> IF(K$3&lt;&gt;$D8, MID($C8,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L8" s="20" t="str" cm="1">
+      <c r="L8" s="16" t="str" cm="1">
         <f t="array" ref="L8" xml:space="preserve"> IF(L$3&lt;&gt;$D8, MID($C8,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M8" s="21" t="str" cm="1">
+      <c r="M8" s="17" t="str" cm="1">
         <f t="array" ref="M8" xml:space="preserve"> IF(M$3&lt;&gt;$D8, MID($C8,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C8,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1508,49 +1508,49 @@
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E9" s="20" t="str" cm="1">
+      <c r="E9" s="16" t="str" cm="1">
         <f t="array" ref="E9" xml:space="preserve"> IF(E$3&lt;&gt;$D9, MID($C9,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>z</v>
       </c>
-      <c r="F9" s="20" t="str" cm="1">
+      <c r="F9" s="16" t="str" cm="1">
         <f t="array" ref="F9" xml:space="preserve"> IF(F$3&lt;&gt;$D9, MID($C9,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G9" s="20" t="str" cm="1">
+      <c r="G9" s="16" t="str" cm="1">
         <f t="array" ref="G9" xml:space="preserve"> IF(G$3&lt;&gt;$D9, MID($C9,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="H9" s="20" t="str" cm="1">
+      <c r="H9" s="16" t="str" cm="1">
         <f t="array" ref="H9" xml:space="preserve"> IF(H$3&lt;&gt;$D9, MID($C9,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I9" s="20" t="str" cm="1">
+      <c r="I9" s="16" t="str" cm="1">
         <f t="array" ref="I9" xml:space="preserve"> IF(I$3&lt;&gt;$D9, MID($C9,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J9" s="20" t="str" cm="1">
+      <c r="J9" s="16" t="str" cm="1">
         <f t="array" ref="J9" xml:space="preserve"> IF(J$3&lt;&gt;$D9, MID($C9,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K9" s="20" t="str" cm="1">
+      <c r="K9" s="16" t="str" cm="1">
         <f t="array" ref="K9" xml:space="preserve"> IF(K$3&lt;&gt;$D9, MID($C9,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L9" s="20" t="str" cm="1">
+      <c r="L9" s="16" t="str" cm="1">
         <f t="array" ref="L9" xml:space="preserve"> IF(L$3&lt;&gt;$D9, MID($C9,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M9" s="21" t="str" cm="1">
+      <c r="M9" s="17" t="str" cm="1">
         <f t="array" ref="M9" xml:space="preserve"> IF(M$3&lt;&gt;$D9, MID($C9,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C9,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1558,49 +1558,49 @@
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E10" s="20" t="str" cm="1">
+      <c r="E10" s="16" t="str" cm="1">
         <f t="array" ref="E10" xml:space="preserve"> IF(E$3&lt;&gt;$D10, MID($C10,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F10" s="20" t="str" cm="1">
+      <c r="F10" s="16" t="str" cm="1">
         <f t="array" ref="F10" xml:space="preserve"> IF(F$3&lt;&gt;$D10, MID($C10,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G10" s="20" t="str" cm="1">
+      <c r="G10" s="16" t="str" cm="1">
         <f t="array" ref="G10" xml:space="preserve"> IF(G$3&lt;&gt;$D10, MID($C10,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H10" s="20" t="str" cm="1">
+      <c r="H10" s="16" t="str" cm="1">
         <f t="array" ref="H10" xml:space="preserve"> IF(H$3&lt;&gt;$D10, MID($C10,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I10" s="20" t="str" cm="1">
+      <c r="I10" s="16" t="str" cm="1">
         <f t="array" ref="I10" xml:space="preserve"> IF(I$3&lt;&gt;$D10, MID($C10,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>_</v>
       </c>
-      <c r="J10" s="20" t="str" cm="1">
+      <c r="J10" s="16" t="str" cm="1">
         <f t="array" ref="J10" xml:space="preserve"> IF(J$3&lt;&gt;$D10, MID($C10,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K10" s="20" t="str" cm="1">
+      <c r="K10" s="16" t="str" cm="1">
         <f t="array" ref="K10" xml:space="preserve"> IF(K$3&lt;&gt;$D10, MID($C10,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L10" s="20" t="str" cm="1">
+      <c r="L10" s="16" t="str" cm="1">
         <f t="array" ref="L10" xml:space="preserve"> IF(L$3&lt;&gt;$D10, MID($C10,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M10" s="21" t="str" cm="1">
+      <c r="M10" s="17" t="str" cm="1">
         <f t="array" ref="M10" xml:space="preserve"> IF(M$3&lt;&gt;$D10, MID($C10,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C10,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1608,45 +1608,45 @@
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="20" t="str" cm="1">
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="16" t="str" cm="1">
         <f t="array" ref="E11" xml:space="preserve"> IF(E$3&lt;&gt;$D11, MID($C11,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="F11" s="20" t="str" cm="1">
+      <c r="F11" s="16" t="str" cm="1">
         <f t="array" ref="F11" xml:space="preserve"> IF(F$3&lt;&gt;$D11, MID($C11,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G11" s="20" t="str" cm="1">
+      <c r="G11" s="16" t="str" cm="1">
         <f t="array" ref="G11" xml:space="preserve"> IF(G$3&lt;&gt;$D11, MID($C11,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H11" s="20" t="str" cm="1">
+      <c r="H11" s="16" t="str" cm="1">
         <f t="array" ref="H11" xml:space="preserve"> IF(H$3&lt;&gt;$D11, MID($C11,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I11" s="20" t="str" cm="1">
+      <c r="I11" s="16" t="str" cm="1">
         <f t="array" ref="I11" xml:space="preserve"> IF(I$3&lt;&gt;$D11, MID($C11,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J11" s="20" t="str" cm="1">
+      <c r="J11" s="16" t="str" cm="1">
         <f t="array" ref="J11" xml:space="preserve"> IF(J$3&lt;&gt;$D11, MID($C11,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K11" s="20" t="str" cm="1">
+      <c r="K11" s="16" t="str" cm="1">
         <f t="array" ref="K11" xml:space="preserve"> IF(K$3&lt;&gt;$D11, MID($C11,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L11" s="20" t="str" cm="1">
+      <c r="L11" s="16" t="str" cm="1">
         <f t="array" ref="L11" xml:space="preserve"> IF(L$3&lt;&gt;$D11, MID($C11,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M11" s="21" t="str" cm="1">
+      <c r="M11" s="17" t="str" cm="1">
         <f t="array" ref="M11" xml:space="preserve"> IF(M$3&lt;&gt;$D11, MID($C11,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C11,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1654,49 +1654,49 @@
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E12" s="20" t="str" cm="1">
+      <c r="E12" s="16" t="str" cm="1">
         <f t="array" ref="E12" xml:space="preserve"> IF(E$3&lt;&gt;$D12, MID($C12,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F12" s="20" t="str" cm="1">
+      <c r="F12" s="16" t="str" cm="1">
         <f t="array" ref="F12" xml:space="preserve"> IF(F$3&lt;&gt;$D12, MID($C12,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G12" s="20" t="str" cm="1">
+      <c r="G12" s="16" t="str" cm="1">
         <f t="array" ref="G12" xml:space="preserve"> IF(G$3&lt;&gt;$D12, MID($C12,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H12" s="20" t="str" cm="1">
+      <c r="H12" s="16" t="str" cm="1">
         <f t="array" ref="H12" xml:space="preserve"> IF(H$3&lt;&gt;$D12, MID($C12,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="I12" s="20" t="str" cm="1">
+      <c r="I12" s="16" t="str" cm="1">
         <f t="array" ref="I12" xml:space="preserve"> IF(I$3&lt;&gt;$D12, MID($C12,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="J12" s="20" t="str" cm="1">
+      <c r="J12" s="16" t="str" cm="1">
         <f t="array" ref="J12" xml:space="preserve"> IF(J$3&lt;&gt;$D12, MID($C12,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K12" s="20" t="str" cm="1">
+      <c r="K12" s="16" t="str" cm="1">
         <f t="array" ref="K12" xml:space="preserve"> IF(K$3&lt;&gt;$D12, MID($C12,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L12" s="20" t="str" cm="1">
+      <c r="L12" s="16" t="str" cm="1">
         <f t="array" ref="L12" xml:space="preserve"> IF(L$3&lt;&gt;$D12, MID($C12,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M12" s="21" t="str" cm="1">
+      <c r="M12" s="17" t="str" cm="1">
         <f t="array" ref="M12" xml:space="preserve"> IF(M$3&lt;&gt;$D12, MID($C12,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C12,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1704,49 +1704,49 @@
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E13" s="20" t="str" cm="1">
+      <c r="E13" s="16" t="str" cm="1">
         <f t="array" ref="E13" xml:space="preserve"> IF(E$3&lt;&gt;$D13, MID($C13,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F13" s="20" t="str" cm="1">
+      <c r="F13" s="16" t="str" cm="1">
         <f t="array" ref="F13" xml:space="preserve"> IF(F$3&lt;&gt;$D13, MID($C13,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G13" s="20" t="str" cm="1">
+      <c r="G13" s="16" t="str" cm="1">
         <f t="array" ref="G13" xml:space="preserve"> IF(G$3&lt;&gt;$D13, MID($C13,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="H13" s="20" t="str" cm="1">
+      <c r="H13" s="16" t="str" cm="1">
         <f t="array" ref="H13" xml:space="preserve"> IF(H$3&lt;&gt;$D13, MID($C13,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I13" s="20" t="str" cm="1">
+      <c r="I13" s="16" t="str" cm="1">
         <f t="array" ref="I13" xml:space="preserve"> IF(I$3&lt;&gt;$D13, MID($C13,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J13" s="20" t="str" cm="1">
+      <c r="J13" s="16" t="str" cm="1">
         <f t="array" ref="J13" xml:space="preserve"> IF(J$3&lt;&gt;$D13, MID($C13,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K13" s="20" t="str" cm="1">
+      <c r="K13" s="16" t="str" cm="1">
         <f t="array" ref="K13" xml:space="preserve"> IF(K$3&lt;&gt;$D13, MID($C13,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L13" s="20" t="str" cm="1">
+      <c r="L13" s="16" t="str" cm="1">
         <f t="array" ref="L13" xml:space="preserve"> IF(L$3&lt;&gt;$D13, MID($C13,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M13" s="21" t="str" cm="1">
+      <c r="M13" s="17" t="str" cm="1">
         <f t="array" ref="M13" xml:space="preserve"> IF(M$3&lt;&gt;$D13, MID($C13,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C13,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1754,49 +1754,49 @@
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E14" s="20" t="str" cm="1">
+      <c r="E14" s="16" t="str" cm="1">
         <f t="array" ref="E14" xml:space="preserve"> IF(E$3&lt;&gt;$D14, MID($C14,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="F14" s="20" t="str" cm="1">
+      <c r="F14" s="16" t="str" cm="1">
         <f t="array" ref="F14" xml:space="preserve"> IF(F$3&lt;&gt;$D14, MID($C14,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="G14" s="20" t="str" cm="1">
+      <c r="G14" s="16" t="str" cm="1">
         <f t="array" ref="G14" xml:space="preserve"> IF(G$3&lt;&gt;$D14, MID($C14,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H14" s="20" t="str" cm="1">
+      <c r="H14" s="16" t="str" cm="1">
         <f t="array" ref="H14" xml:space="preserve"> IF(H$3&lt;&gt;$D14, MID($C14,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>\</v>
       </c>
-      <c r="I14" s="20" t="str" cm="1">
+      <c r="I14" s="16" t="str" cm="1">
         <f t="array" ref="I14" xml:space="preserve"> IF(I$3&lt;&gt;$D14, MID($C14,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J14" s="20" t="str" cm="1">
+      <c r="J14" s="16" t="str" cm="1">
         <f t="array" ref="J14" xml:space="preserve"> IF(J$3&lt;&gt;$D14, MID($C14,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K14" s="20" t="str" cm="1">
+      <c r="K14" s="16" t="str" cm="1">
         <f t="array" ref="K14" xml:space="preserve"> IF(K$3&lt;&gt;$D14, MID($C14,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L14" s="20" t="str" cm="1">
+      <c r="L14" s="16" t="str" cm="1">
         <f t="array" ref="L14" xml:space="preserve"> IF(L$3&lt;&gt;$D14, MID($C14,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M14" s="21" t="str" cm="1">
+      <c r="M14" s="17" t="str" cm="1">
         <f t="array" ref="M14" xml:space="preserve"> IF(M$3&lt;&gt;$D14, MID($C14,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C14,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1804,49 +1804,49 @@
       <c r="P14" s="2"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="15">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E15" s="20" t="str" cm="1">
+      <c r="E15" s="16" t="str" cm="1">
         <f t="array" ref="E15" xml:space="preserve"> IF(E$3&lt;&gt;$D15, MID($C15,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="F15" s="20" t="str" cm="1">
+      <c r="F15" s="16" t="str" cm="1">
         <f t="array" ref="F15" xml:space="preserve"> IF(F$3&lt;&gt;$D15, MID($C15,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G15" s="20" t="str" cm="1">
+      <c r="G15" s="16" t="str" cm="1">
         <f t="array" ref="G15" xml:space="preserve"> IF(G$3&lt;&gt;$D15, MID($C15,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H15" s="20" t="str" cm="1">
+      <c r="H15" s="16" t="str" cm="1">
         <f t="array" ref="H15" xml:space="preserve"> IF(H$3&lt;&gt;$D15, MID($C15,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I15" s="20" t="str" cm="1">
+      <c r="I15" s="16" t="str" cm="1">
         <f t="array" ref="I15" xml:space="preserve"> IF(I$3&lt;&gt;$D15, MID($C15,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J15" s="20" t="str" cm="1">
+      <c r="J15" s="16" t="str" cm="1">
         <f t="array" ref="J15" xml:space="preserve"> IF(J$3&lt;&gt;$D15, MID($C15,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>\</v>
       </c>
-      <c r="K15" s="20" t="str" cm="1">
+      <c r="K15" s="16" t="str" cm="1">
         <f t="array" ref="K15" xml:space="preserve"> IF(K$3&lt;&gt;$D15, MID($C15,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L15" s="20" t="str" cm="1">
+      <c r="L15" s="16" t="str" cm="1">
         <f t="array" ref="L15" xml:space="preserve"> IF(L$3&lt;&gt;$D15, MID($C15,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M15" s="21" t="str" cm="1">
+      <c r="M15" s="17" t="str" cm="1">
         <f t="array" ref="M15" xml:space="preserve"> IF(M$3&lt;&gt;$D15, MID($C15,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C15,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1854,49 +1854,49 @@
       <c r="P15" s="2"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E16" s="20" t="str" cm="1">
+      <c r="E16" s="16" t="str" cm="1">
         <f t="array" ref="E16" xml:space="preserve"> IF(E$3&lt;&gt;$D16, MID($C16,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="F16" s="20" t="str" cm="1">
+      <c r="F16" s="16" t="str" cm="1">
         <f t="array" ref="F16" xml:space="preserve"> IF(F$3&lt;&gt;$D16, MID($C16,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G16" s="20" t="str" cm="1">
+      <c r="G16" s="16" t="str" cm="1">
         <f t="array" ref="G16" xml:space="preserve"> IF(G$3&lt;&gt;$D16, MID($C16,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="H16" s="20" t="str" cm="1">
+      <c r="H16" s="16" t="str" cm="1">
         <f t="array" ref="H16" xml:space="preserve"> IF(H$3&lt;&gt;$D16, MID($C16,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>]</v>
       </c>
-      <c r="I16" s="20" t="str" cm="1">
+      <c r="I16" s="16" t="str" cm="1">
         <f t="array" ref="I16" xml:space="preserve"> IF(I$3&lt;&gt;$D16, MID($C16,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J16" s="20" t="str" cm="1">
+      <c r="J16" s="16" t="str" cm="1">
         <f t="array" ref="J16" xml:space="preserve"> IF(J$3&lt;&gt;$D16, MID($C16,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K16" s="20" t="str" cm="1">
+      <c r="K16" s="16" t="str" cm="1">
         <f t="array" ref="K16" xml:space="preserve"> IF(K$3&lt;&gt;$D16, MID($C16,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L16" s="20" t="str" cm="1">
+      <c r="L16" s="16" t="str" cm="1">
         <f t="array" ref="L16" xml:space="preserve"> IF(L$3&lt;&gt;$D16, MID($C16,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M16" s="21" t="str" cm="1">
+      <c r="M16" s="17" t="str" cm="1">
         <f t="array" ref="M16" xml:space="preserve"> IF(M$3&lt;&gt;$D16, MID($C16,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C16,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1904,49 +1904,49 @@
       <c r="P16" s="2"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E17" s="20" t="str" cm="1">
+      <c r="E17" s="16" t="str" cm="1">
         <f t="array" ref="E17" xml:space="preserve"> IF(E$3&lt;&gt;$D17, MID($C17,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F17" s="20" t="str" cm="1">
+      <c r="F17" s="16" t="str" cm="1">
         <f t="array" ref="F17" xml:space="preserve"> IF(F$3&lt;&gt;$D17, MID($C17,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G17" s="20" t="str" cm="1">
+      <c r="G17" s="16" t="str" cm="1">
         <f t="array" ref="G17" xml:space="preserve"> IF(G$3&lt;&gt;$D17, MID($C17,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H17" s="20" t="str" cm="1">
+      <c r="H17" s="16" t="str" cm="1">
         <f t="array" ref="H17" xml:space="preserve"> IF(H$3&lt;&gt;$D17, MID($C17,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="I17" s="20" t="str" cm="1">
+      <c r="I17" s="16" t="str" cm="1">
         <f t="array" ref="I17" xml:space="preserve"> IF(I$3&lt;&gt;$D17, MID($C17,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J17" s="20" t="str" cm="1">
+      <c r="J17" s="16" t="str" cm="1">
         <f t="array" ref="J17" xml:space="preserve"> IF(J$3&lt;&gt;$D17, MID($C17,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K17" s="20" t="str" cm="1">
+      <c r="K17" s="16" t="str" cm="1">
         <f t="array" ref="K17" xml:space="preserve"> IF(K$3&lt;&gt;$D17, MID($C17,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L17" s="20" t="str" cm="1">
+      <c r="L17" s="16" t="str" cm="1">
         <f t="array" ref="L17" xml:space="preserve"> IF(L$3&lt;&gt;$D17, MID($C17,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M17" s="21" t="str" cm="1">
+      <c r="M17" s="17" t="str" cm="1">
         <f t="array" ref="M17" xml:space="preserve"> IF(M$3&lt;&gt;$D17, MID($C17,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C17,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -1954,49 +1954,49 @@
       <c r="P17" s="2"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E18" s="20" t="str" cm="1">
+      <c r="E18" s="16" t="str" cm="1">
         <f t="array" ref="E18" xml:space="preserve"> IF(E$3&lt;&gt;$D18, MID($C18,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="F18" s="20" t="str" cm="1">
+      <c r="F18" s="16" t="str" cm="1">
         <f t="array" ref="F18" xml:space="preserve"> IF(F$3&lt;&gt;$D18, MID($C18,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="G18" s="20" t="str" cm="1">
+      <c r="G18" s="16" t="str" cm="1">
         <f t="array" ref="G18" xml:space="preserve"> IF(G$3&lt;&gt;$D18, MID($C18,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H18" s="20" t="str" cm="1">
+      <c r="H18" s="16" t="str" cm="1">
         <f t="array" ref="H18" xml:space="preserve"> IF(H$3&lt;&gt;$D18, MID($C18,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="I18" s="20" t="str" cm="1">
+      <c r="I18" s="16" t="str" cm="1">
         <f t="array" ref="I18" xml:space="preserve"> IF(I$3&lt;&gt;$D18, MID($C18,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J18" s="20" t="str" cm="1">
+      <c r="J18" s="16" t="str" cm="1">
         <f t="array" ref="J18" xml:space="preserve"> IF(J$3&lt;&gt;$D18, MID($C18,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K18" s="20" t="str" cm="1">
+      <c r="K18" s="16" t="str" cm="1">
         <f t="array" ref="K18" xml:space="preserve"> IF(K$3&lt;&gt;$D18, MID($C18,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L18" s="20" t="str" cm="1">
+      <c r="L18" s="16" t="str" cm="1">
         <f t="array" ref="L18" xml:space="preserve"> IF(L$3&lt;&gt;$D18, MID($C18,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M18" s="21" t="str" cm="1">
+      <c r="M18" s="17" t="str" cm="1">
         <f t="array" ref="M18" xml:space="preserve"> IF(M$3&lt;&gt;$D18, MID($C18,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C18,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2004,45 +2004,45 @@
       <c r="P18" s="2"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="20" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="20" t="str" cm="1">
+      <c r="G19" s="16" t="str" cm="1">
         <f t="array" ref="G19" xml:space="preserve"> IF(G$3&lt;&gt;$D19, MID($C19,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H19" s="20" t="str" cm="1">
+      <c r="H19" s="16" t="str" cm="1">
         <f t="array" ref="H19" xml:space="preserve"> IF(H$3&lt;&gt;$D19, MID($C19,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I19" s="20" t="str" cm="1">
+      <c r="I19" s="16" t="str" cm="1">
         <f t="array" ref="I19" xml:space="preserve"> IF(I$3&lt;&gt;$D19, MID($C19,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J19" s="20" t="str" cm="1">
+      <c r="J19" s="16" t="str" cm="1">
         <f t="array" ref="J19" xml:space="preserve"> IF(J$3&lt;&gt;$D19, MID($C19,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K19" s="20" t="str" cm="1">
+      <c r="K19" s="16" t="str" cm="1">
         <f t="array" ref="K19" xml:space="preserve"> IF(K$3&lt;&gt;$D19, MID($C19,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L19" s="20" t="str" cm="1">
+      <c r="L19" s="16" t="str" cm="1">
         <f t="array" ref="L19" xml:space="preserve"> IF(L$3&lt;&gt;$D19, MID($C19,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M19" s="21" t="str" cm="1">
+      <c r="M19" s="17" t="str" cm="1">
         <f t="array" ref="M19" xml:space="preserve"> IF(M$3&lt;&gt;$D19, MID($C19,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C19,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2050,49 +2050,49 @@
       <c r="P19" s="2"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E20" s="20" t="str" cm="1">
+      <c r="E20" s="16" t="str" cm="1">
         <f t="array" ref="E20" xml:space="preserve"> IF(E$3&lt;&gt;$D20, MID($C20,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="F20" s="20" t="str" cm="1">
+      <c r="F20" s="16" t="str" cm="1">
         <f t="array" ref="F20" xml:space="preserve"> IF(F$3&lt;&gt;$D20, MID($C20,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G20" s="20" t="str" cm="1">
+      <c r="G20" s="16" t="str" cm="1">
         <f t="array" ref="G20" xml:space="preserve"> IF(G$3&lt;&gt;$D20, MID($C20,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>[</v>
       </c>
-      <c r="H20" s="20" t="str" cm="1">
+      <c r="H20" s="16" t="str" cm="1">
         <f t="array" ref="H20" xml:space="preserve"> IF(H$3&lt;&gt;$D20, MID($C20,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I20" s="20" t="str" cm="1">
+      <c r="I20" s="16" t="str" cm="1">
         <f t="array" ref="I20" xml:space="preserve"> IF(I$3&lt;&gt;$D20, MID($C20,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J20" s="20" t="str" cm="1">
+      <c r="J20" s="16" t="str" cm="1">
         <f t="array" ref="J20" xml:space="preserve"> IF(J$3&lt;&gt;$D20, MID($C20,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K20" s="20" t="str" cm="1">
+      <c r="K20" s="16" t="str" cm="1">
         <f t="array" ref="K20" xml:space="preserve"> IF(K$3&lt;&gt;$D20, MID($C20,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L20" s="20" t="str" cm="1">
+      <c r="L20" s="16" t="str" cm="1">
         <f t="array" ref="L20" xml:space="preserve"> IF(L$3&lt;&gt;$D20, MID($C20,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M20" s="21" t="str" cm="1">
+      <c r="M20" s="17" t="str" cm="1">
         <f t="array" ref="M20" xml:space="preserve"> IF(M$3&lt;&gt;$D20, MID($C20,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C20,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2100,49 +2100,49 @@
       <c r="P20" s="2"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="15">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E21" s="20" t="str" cm="1">
+      <c r="E21" s="16" t="str" cm="1">
         <f t="array" ref="E21" xml:space="preserve"> IF(E$3&lt;&gt;$D21, MID($C21,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="F21" s="20" t="str" cm="1">
+      <c r="F21" s="16" t="str" cm="1">
         <f t="array" ref="F21" xml:space="preserve"> IF(F$3&lt;&gt;$D21, MID($C21,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G21" s="20" t="str" cm="1">
+      <c r="G21" s="16" t="str" cm="1">
         <f t="array" ref="G21" xml:space="preserve"> IF(G$3&lt;&gt;$D21, MID($C21,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H21" s="20" t="str" cm="1">
+      <c r="H21" s="16" t="str" cm="1">
         <f t="array" ref="H21" xml:space="preserve"> IF(H$3&lt;&gt;$D21, MID($C21,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="I21" s="20" t="str" cm="1">
+      <c r="I21" s="16" t="str" cm="1">
         <f t="array" ref="I21" xml:space="preserve"> IF(I$3&lt;&gt;$D21, MID($C21,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J21" s="20" t="str" cm="1">
+      <c r="J21" s="16" t="str" cm="1">
         <f t="array" ref="J21" xml:space="preserve"> IF(J$3&lt;&gt;$D21, MID($C21,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>_</v>
       </c>
-      <c r="K21" s="20" t="str" cm="1">
+      <c r="K21" s="16" t="str" cm="1">
         <f t="array" ref="K21" xml:space="preserve"> IF(K$3&lt;&gt;$D21, MID($C21,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L21" s="20" t="str" cm="1">
+      <c r="L21" s="16" t="str" cm="1">
         <f t="array" ref="L21" xml:space="preserve"> IF(L$3&lt;&gt;$D21, MID($C21,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M21" s="21" t="str" cm="1">
+      <c r="M21" s="17" t="str" cm="1">
         <f t="array" ref="M21" xml:space="preserve"> IF(M$3&lt;&gt;$D21, MID($C21,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C21,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2150,49 +2150,49 @@
       <c r="P21" s="2"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E22" s="20" t="str" cm="1">
+      <c r="E22" s="16" t="str" cm="1">
         <f t="array" ref="E22" xml:space="preserve"> IF(E$3&lt;&gt;$D22, MID($C22,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="F22" s="20" t="str" cm="1">
+      <c r="F22" s="16" t="str" cm="1">
         <f t="array" ref="F22" xml:space="preserve"> IF(F$3&lt;&gt;$D22, MID($C22,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G22" s="20" t="str" cm="1">
+      <c r="G22" s="16" t="str" cm="1">
         <f t="array" ref="G22" xml:space="preserve"> IF(G$3&lt;&gt;$D22, MID($C22,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H22" s="20" t="str" cm="1">
+      <c r="H22" s="16" t="str" cm="1">
         <f t="array" ref="H22" xml:space="preserve"> IF(H$3&lt;&gt;$D22, MID($C22,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="I22" s="20" t="str" cm="1">
+      <c r="I22" s="16" t="str" cm="1">
         <f t="array" ref="I22" xml:space="preserve"> IF(I$3&lt;&gt;$D22, MID($C22,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J22" s="20" t="str" cm="1">
+      <c r="J22" s="16" t="str" cm="1">
         <f t="array" ref="J22" xml:space="preserve"> IF(J$3&lt;&gt;$D22, MID($C22,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K22" s="20" t="str" cm="1">
+      <c r="K22" s="16" t="str" cm="1">
         <f t="array" ref="K22" xml:space="preserve"> IF(K$3&lt;&gt;$D22, MID($C22,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L22" s="20" t="str" cm="1">
+      <c r="L22" s="16" t="str" cm="1">
         <f t="array" ref="L22" xml:space="preserve"> IF(L$3&lt;&gt;$D22, MID($C22,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M22" s="21" t="str" cm="1">
+      <c r="M22" s="17" t="str" cm="1">
         <f t="array" ref="M22" xml:space="preserve"> IF(M$3&lt;&gt;$D22, MID($C22,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C22,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2200,49 +2200,49 @@
       <c r="P22" s="2"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E23" s="20" t="str" cm="1">
+      <c r="E23" s="16" t="str" cm="1">
         <f t="array" ref="E23" xml:space="preserve"> IF(E$3&lt;&gt;$D23, MID($C23,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="F23" s="20" t="str" cm="1">
+      <c r="F23" s="16" t="str" cm="1">
         <f t="array" ref="F23" xml:space="preserve"> IF(F$3&lt;&gt;$D23, MID($C23,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G23" s="20" t="str" cm="1">
+      <c r="G23" s="16" t="str" cm="1">
         <f t="array" ref="G23" xml:space="preserve"> IF(G$3&lt;&gt;$D23, MID($C23,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H23" s="20" t="str" cm="1">
+      <c r="H23" s="16" t="str" cm="1">
         <f t="array" ref="H23" xml:space="preserve"> IF(H$3&lt;&gt;$D23, MID($C23,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="I23" s="20" t="str" cm="1">
+      <c r="I23" s="16" t="str" cm="1">
         <f t="array" ref="I23" xml:space="preserve"> IF(I$3&lt;&gt;$D23, MID($C23,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="J23" s="20" t="str" cm="1">
+      <c r="J23" s="16" t="str" cm="1">
         <f t="array" ref="J23" xml:space="preserve"> IF(J$3&lt;&gt;$D23, MID($C23,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K23" s="20" t="str" cm="1">
+      <c r="K23" s="16" t="str" cm="1">
         <f t="array" ref="K23" xml:space="preserve"> IF(K$3&lt;&gt;$D23, MID($C23,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L23" s="20" t="str" cm="1">
+      <c r="L23" s="16" t="str" cm="1">
         <f t="array" ref="L23" xml:space="preserve"> IF(L$3&lt;&gt;$D23, MID($C23,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M23" s="21" t="str" cm="1">
+      <c r="M23" s="17" t="str" cm="1">
         <f t="array" ref="M23" xml:space="preserve"> IF(M$3&lt;&gt;$D23, MID($C23,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C23,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2250,49 +2250,49 @@
       <c r="P23" s="2"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E24" s="20" t="str" cm="1">
+      <c r="E24" s="16" t="str" cm="1">
         <f t="array" ref="E24" xml:space="preserve"> IF(E$3&lt;&gt;$D24, MID($C24,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>b</v>
       </c>
-      <c r="F24" s="20" t="str" cm="1">
+      <c r="F24" s="16" t="str" cm="1">
         <f t="array" ref="F24" xml:space="preserve"> IF(F$3&lt;&gt;$D24, MID($C24,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="G24" s="20" t="str" cm="1">
+      <c r="G24" s="16" t="str" cm="1">
         <f t="array" ref="G24" xml:space="preserve"> IF(G$3&lt;&gt;$D24, MID($C24,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H24" s="20" t="str" cm="1">
+      <c r="H24" s="16" t="str" cm="1">
         <f t="array" ref="H24" xml:space="preserve"> IF(H$3&lt;&gt;$D24, MID($C24,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>-</v>
       </c>
-      <c r="I24" s="20" t="str" cm="1">
+      <c r="I24" s="16" t="str" cm="1">
         <f t="array" ref="I24" xml:space="preserve"> IF(I$3&lt;&gt;$D24, MID($C24,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J24" s="20" t="str" cm="1">
+      <c r="J24" s="16" t="str" cm="1">
         <f t="array" ref="J24" xml:space="preserve"> IF(J$3&lt;&gt;$D24, MID($C24,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K24" s="20" t="str" cm="1">
+      <c r="K24" s="16" t="str" cm="1">
         <f t="array" ref="K24" xml:space="preserve"> IF(K$3&lt;&gt;$D24, MID($C24,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L24" s="20" t="str" cm="1">
+      <c r="L24" s="16" t="str" cm="1">
         <f t="array" ref="L24" xml:space="preserve"> IF(L$3&lt;&gt;$D24, MID($C24,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M24" s="21" t="str" cm="1">
+      <c r="M24" s="17" t="str" cm="1">
         <f t="array" ref="M24" xml:space="preserve"> IF(M$3&lt;&gt;$D24, MID($C24,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C24,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2300,49 +2300,49 @@
       <c r="P24" s="2"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E25" s="20" t="str" cm="1">
+      <c r="E25" s="16" t="str" cm="1">
         <f t="array" ref="E25" xml:space="preserve"> IF(E$3&lt;&gt;$D25, MID($C25,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>j</v>
       </c>
-      <c r="F25" s="20" t="str" cm="1">
+      <c r="F25" s="16" t="str" cm="1">
         <f t="array" ref="F25" xml:space="preserve"> IF(F$3&lt;&gt;$D25, MID($C25,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G25" s="20" t="str" cm="1">
+      <c r="G25" s="16" t="str" cm="1">
         <f t="array" ref="G25" xml:space="preserve"> IF(G$3&lt;&gt;$D25, MID($C25,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H25" s="20" t="str" cm="1">
+      <c r="H25" s="16" t="str" cm="1">
         <f t="array" ref="H25" xml:space="preserve"> IF(H$3&lt;&gt;$D25, MID($C25,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>-</v>
       </c>
-      <c r="I25" s="20" t="str" cm="1">
+      <c r="I25" s="16" t="str" cm="1">
         <f t="array" ref="I25" xml:space="preserve"> IF(I$3&lt;&gt;$D25, MID($C25,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J25" s="20" t="str" cm="1">
+      <c r="J25" s="16" t="str" cm="1">
         <f t="array" ref="J25" xml:space="preserve"> IF(J$3&lt;&gt;$D25, MID($C25,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K25" s="20" t="str" cm="1">
+      <c r="K25" s="16" t="str" cm="1">
         <f t="array" ref="K25" xml:space="preserve"> IF(K$3&lt;&gt;$D25, MID($C25,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L25" s="20" t="str" cm="1">
+      <c r="L25" s="16" t="str" cm="1">
         <f t="array" ref="L25" xml:space="preserve"> IF(L$3&lt;&gt;$D25, MID($C25,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M25" s="21" t="str" cm="1">
+      <c r="M25" s="17" t="str" cm="1">
         <f t="array" ref="M25" xml:space="preserve"> IF(M$3&lt;&gt;$D25, MID($C25,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C25,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2350,49 +2350,49 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E26" s="20" t="str" cm="1">
+      <c r="E26" s="16" t="str" cm="1">
         <f t="array" ref="E26" xml:space="preserve"> IF(E$3&lt;&gt;$D26, MID($C26,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="F26" s="20" t="str" cm="1">
+      <c r="F26" s="16" t="str" cm="1">
         <f t="array" ref="F26" xml:space="preserve"> IF(F$3&lt;&gt;$D26, MID($C26,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="G26" s="20" t="str" cm="1">
+      <c r="G26" s="16" t="str" cm="1">
         <f t="array" ref="G26" xml:space="preserve"> IF(G$3&lt;&gt;$D26, MID($C26,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H26" s="20" t="str" cm="1">
+      <c r="H26" s="16" t="str" cm="1">
         <f t="array" ref="H26" xml:space="preserve"> IF(H$3&lt;&gt;$D26, MID($C26,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="I26" s="20" t="str" cm="1">
+      <c r="I26" s="16" t="str" cm="1">
         <f t="array" ref="I26" xml:space="preserve"> IF(I$3&lt;&gt;$D26, MID($C26,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J26" s="20" t="str" cm="1">
+      <c r="J26" s="16" t="str" cm="1">
         <f t="array" ref="J26" xml:space="preserve"> IF(J$3&lt;&gt;$D26, MID($C26,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K26" s="20" t="str" cm="1">
+      <c r="K26" s="16" t="str" cm="1">
         <f t="array" ref="K26" xml:space="preserve"> IF(K$3&lt;&gt;$D26, MID($C26,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L26" s="20" t="str" cm="1">
+      <c r="L26" s="16" t="str" cm="1">
         <f t="array" ref="L26" xml:space="preserve"> IF(L$3&lt;&gt;$D26, MID($C26,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M26" s="21" t="str" cm="1">
+      <c r="M26" s="17" t="str" cm="1">
         <f t="array" ref="M26" xml:space="preserve"> IF(M$3&lt;&gt;$D26, MID($C26,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C26,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2400,45 +2400,45 @@
       <c r="P26" s="2"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="20" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G27" s="20" t="str" cm="1">
+      <c r="G27" s="16" t="str" cm="1">
         <f t="array" ref="G27" xml:space="preserve"> IF(G$3&lt;&gt;$D27, MID($C27,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H27" s="20" t="str" cm="1">
+      <c r="H27" s="16" t="str" cm="1">
         <f t="array" ref="H27" xml:space="preserve"> IF(H$3&lt;&gt;$D27, MID($C27,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I27" s="20" t="str" cm="1">
+      <c r="I27" s="16" t="str" cm="1">
         <f t="array" ref="I27" xml:space="preserve"> IF(I$3&lt;&gt;$D27, MID($C27,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J27" s="20" t="str" cm="1">
+      <c r="J27" s="16" t="str" cm="1">
         <f t="array" ref="J27" xml:space="preserve"> IF(J$3&lt;&gt;$D27, MID($C27,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K27" s="20" t="str" cm="1">
+      <c r="K27" s="16" t="str" cm="1">
         <f t="array" ref="K27" xml:space="preserve"> IF(K$3&lt;&gt;$D27, MID($C27,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L27" s="20" t="str" cm="1">
+      <c r="L27" s="16" t="str" cm="1">
         <f t="array" ref="L27" xml:space="preserve"> IF(L$3&lt;&gt;$D27, MID($C27,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M27" s="21" t="str" cm="1">
+      <c r="M27" s="17" t="str" cm="1">
         <f t="array" ref="M27" xml:space="preserve"> IF(M$3&lt;&gt;$D27, MID($C27,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C27,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2446,93 +2446,93 @@
       <c r="P27" s="2"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="20" t="str" cm="1">
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E28" s="16" t="str" cm="1">
         <f t="array" ref="E28" xml:space="preserve"> IF(E$3&lt;&gt;$D28, MID($C28,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="F28" s="20" t="str" cm="1">
+      <c r="F28" s="16" t="str" cm="1">
         <f t="array" ref="F28" xml:space="preserve"> IF(F$3&lt;&gt;$D28, MID($C28,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G28" s="20" t="str" cm="1">
+      <c r="G28" s="16" t="str" cm="1">
         <f t="array" ref="G28" xml:space="preserve"> IF(G$3&lt;&gt;$D28, MID($C28,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H28" s="20" t="str" cm="1">
+      <c r="H28" s="16" t="str" cm="1">
         <f t="array" ref="H28" xml:space="preserve"> IF(H$3&lt;&gt;$D28, MID($C28,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I28" s="20" t="str" cm="1">
+      <c r="I28" s="16" t="str" cm="1">
         <f t="array" ref="I28" xml:space="preserve"> IF(I$3&lt;&gt;$D28, MID($C28,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J28" s="20" t="str" cm="1">
+      <c r="J28" s="16" t="str" cm="1">
         <f t="array" ref="J28" xml:space="preserve"> IF(J$3&lt;&gt;$D28, MID($C28,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K28" s="20" t="str" cm="1">
+      <c r="K28" s="16" t="str" cm="1">
         <f t="array" ref="K28" xml:space="preserve"> IF(K$3&lt;&gt;$D28, MID($C28,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L28" s="20" t="str" cm="1">
+      <c r="L28" s="16" t="str" cm="1">
         <f t="array" ref="L28" xml:space="preserve"> IF(L$3&lt;&gt;$D28, MID($C28,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M28" s="21" t="str" cm="1">
+      <c r="M28" s="17" t="str" cm="1">
         <f t="array" ref="M28" xml:space="preserve"> IF(M$3&lt;&gt;$D28, MID($C28,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C28,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E29" s="20" t="str" cm="1">
+      <c r="E29" s="16" t="str" cm="1">
         <f t="array" ref="E29" xml:space="preserve"> IF(E$3&lt;&gt;$D29, MID($C29,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="F29" s="20" t="str" cm="1">
+      <c r="F29" s="16" t="str" cm="1">
         <f t="array" ref="F29" xml:space="preserve"> IF(F$3&lt;&gt;$D29, MID($C29,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G29" s="20" t="str" cm="1">
+      <c r="G29" s="16" t="str" cm="1">
         <f t="array" ref="G29" xml:space="preserve"> IF(G$3&lt;&gt;$D29, MID($C29,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H29" s="20" t="str" cm="1">
+      <c r="H29" s="16" t="str" cm="1">
         <f t="array" ref="H29" xml:space="preserve"> IF(H$3&lt;&gt;$D29, MID($C29,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="I29" s="20" t="str" cm="1">
+      <c r="I29" s="16" t="str" cm="1">
         <f t="array" ref="I29" xml:space="preserve"> IF(I$3&lt;&gt;$D29, MID($C29,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J29" s="20" t="str" cm="1">
+      <c r="J29" s="16" t="str" cm="1">
         <f t="array" ref="J29" xml:space="preserve"> IF(J$3&lt;&gt;$D29, MID($C29,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="K29" s="20" t="str" cm="1">
+      <c r="K29" s="16" t="str" cm="1">
         <f t="array" ref="K29" xml:space="preserve"> IF(K$3&lt;&gt;$D29, MID($C29,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="L29" s="20" t="str" cm="1">
+      <c r="L29" s="16" t="str" cm="1">
         <f t="array" ref="L29" xml:space="preserve"> IF(L$3&lt;&gt;$D29, MID($C29,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M29" s="21" t="str" cm="1">
+      <c r="M29" s="17" t="str" cm="1">
         <f t="array" ref="M29" xml:space="preserve"> IF(M$3&lt;&gt;$D29, MID($C29,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C29,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2540,49 +2540,49 @@
       <c r="P29" s="2"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E30" s="20" t="str" cm="1">
+      <c r="E30" s="16" t="str" cm="1">
         <f t="array" ref="E30" xml:space="preserve"> IF(E$3&lt;&gt;$D30, MID($C30,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="F30" s="20" t="str" cm="1">
+      <c r="F30" s="16" t="str" cm="1">
         <f t="array" ref="F30" xml:space="preserve"> IF(F$3&lt;&gt;$D30, MID($C30,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G30" s="20" t="str" cm="1">
+      <c r="G30" s="16" t="str" cm="1">
         <f t="array" ref="G30" xml:space="preserve"> IF(G$3&lt;&gt;$D30, MID($C30,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="H30" s="20" t="str" cm="1">
+      <c r="H30" s="16" t="str" cm="1">
         <f t="array" ref="H30" xml:space="preserve"> IF(H$3&lt;&gt;$D30, MID($C30,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>]</v>
       </c>
-      <c r="I30" s="20" t="str" cm="1">
+      <c r="I30" s="16" t="str" cm="1">
         <f t="array" ref="I30" xml:space="preserve"> IF(I$3&lt;&gt;$D30, MID($C30,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J30" s="20" t="str" cm="1">
+      <c r="J30" s="16" t="str" cm="1">
         <f t="array" ref="J30" xml:space="preserve"> IF(J$3&lt;&gt;$D30, MID($C30,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K30" s="20" t="str" cm="1">
+      <c r="K30" s="16" t="str" cm="1">
         <f t="array" ref="K30" xml:space="preserve"> IF(K$3&lt;&gt;$D30, MID($C30,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L30" s="20" t="str" cm="1">
+      <c r="L30" s="16" t="str" cm="1">
         <f t="array" ref="L30" xml:space="preserve"> IF(L$3&lt;&gt;$D30, MID($C30,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M30" s="21" t="str" cm="1">
+      <c r="M30" s="17" t="str" cm="1">
         <f t="array" ref="M30" xml:space="preserve"> IF(M$3&lt;&gt;$D30, MID($C30,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C30,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2590,49 +2590,49 @@
       <c r="P30" s="2"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E31" s="20" t="str" cm="1">
+      <c r="E31" s="16" t="str" cm="1">
         <f t="array" ref="E31" xml:space="preserve"> IF(E$3&lt;&gt;$D31, MID($C31,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F31" s="20" t="str" cm="1">
+      <c r="F31" s="16" t="str" cm="1">
         <f t="array" ref="F31" xml:space="preserve"> IF(F$3&lt;&gt;$D31, MID($C31,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G31" s="20" t="str" cm="1">
+      <c r="G31" s="16" t="str" cm="1">
         <f t="array" ref="G31" xml:space="preserve"> IF(G$3&lt;&gt;$D31, MID($C31,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="H31" s="20" t="str" cm="1">
+      <c r="H31" s="16" t="str" cm="1">
         <f t="array" ref="H31" xml:space="preserve"> IF(H$3&lt;&gt;$D31, MID($C31,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I31" s="20" t="str" cm="1">
+      <c r="I31" s="16" t="str" cm="1">
         <f t="array" ref="I31" xml:space="preserve"> IF(I$3&lt;&gt;$D31, MID($C31,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J31" s="20" t="str" cm="1">
+      <c r="J31" s="16" t="str" cm="1">
         <f t="array" ref="J31" xml:space="preserve"> IF(J$3&lt;&gt;$D31, MID($C31,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K31" s="20" t="str" cm="1">
+      <c r="K31" s="16" t="str" cm="1">
         <f t="array" ref="K31" xml:space="preserve"> IF(K$3&lt;&gt;$D31, MID($C31,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L31" s="20" t="str" cm="1">
+      <c r="L31" s="16" t="str" cm="1">
         <f t="array" ref="L31" xml:space="preserve"> IF(L$3&lt;&gt;$D31, MID($C31,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M31" s="21" t="str" cm="1">
+      <c r="M31" s="17" t="str" cm="1">
         <f t="array" ref="M31" xml:space="preserve"> IF(M$3&lt;&gt;$D31, MID($C31,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C31,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2640,49 +2640,49 @@
       <c r="P31" s="2"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E32" s="20" t="str" cm="1">
+      <c r="E32" s="16" t="str" cm="1">
         <f t="array" ref="E32" xml:space="preserve"> IF(E$3&lt;&gt;$D32, MID($C32,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="F32" s="20" t="str" cm="1">
+      <c r="F32" s="16" t="str" cm="1">
         <f t="array" ref="F32" xml:space="preserve"> IF(F$3&lt;&gt;$D32, MID($C32,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G32" s="20" t="str" cm="1">
+      <c r="G32" s="16" t="str" cm="1">
         <f t="array" ref="G32" xml:space="preserve"> IF(G$3&lt;&gt;$D32, MID($C32,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="H32" s="20" t="str" cm="1">
+      <c r="H32" s="16" t="str" cm="1">
         <f t="array" ref="H32" xml:space="preserve"> IF(H$3&lt;&gt;$D32, MID($C32,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I32" s="20" t="str" cm="1">
+      <c r="I32" s="16" t="str" cm="1">
         <f t="array" ref="I32" xml:space="preserve"> IF(I$3&lt;&gt;$D32, MID($C32,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J32" s="20" t="str" cm="1">
+      <c r="J32" s="16" t="str" cm="1">
         <f t="array" ref="J32" xml:space="preserve"> IF(J$3&lt;&gt;$D32, MID($C32,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K32" s="20" t="str" cm="1">
+      <c r="K32" s="16" t="str" cm="1">
         <f t="array" ref="K32" xml:space="preserve"> IF(K$3&lt;&gt;$D32, MID($C32,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L32" s="20" t="str" cm="1">
+      <c r="L32" s="16" t="str" cm="1">
         <f t="array" ref="L32" xml:space="preserve"> IF(L$3&lt;&gt;$D32, MID($C32,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M32" s="21" t="str" cm="1">
+      <c r="M32" s="17" t="str" cm="1">
         <f t="array" ref="M32" xml:space="preserve"> IF(M$3&lt;&gt;$D32, MID($C32,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C32,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2690,49 +2690,49 @@
       <c r="P32" s="2"/>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E33" s="20" t="str" cm="1">
+      <c r="E33" s="16" t="str" cm="1">
         <f t="array" ref="E33" xml:space="preserve"> IF(E$3&lt;&gt;$D33, MID($C33,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="F33" s="20" t="str" cm="1">
+      <c r="F33" s="16" t="str" cm="1">
         <f t="array" ref="F33" xml:space="preserve"> IF(F$3&lt;&gt;$D33, MID($C33,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="G33" s="20" t="str" cm="1">
+      <c r="G33" s="16" t="str" cm="1">
         <f t="array" ref="G33" xml:space="preserve"> IF(G$3&lt;&gt;$D33, MID($C33,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H33" s="20" t="str" cm="1">
+      <c r="H33" s="16" t="str" cm="1">
         <f t="array" ref="H33" xml:space="preserve"> IF(H$3&lt;&gt;$D33, MID($C33,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>_</v>
       </c>
-      <c r="I33" s="20" t="str" cm="1">
+      <c r="I33" s="16" t="str" cm="1">
         <f t="array" ref="I33" xml:space="preserve"> IF(I$3&lt;&gt;$D33, MID($C33,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J33" s="20" t="str" cm="1">
+      <c r="J33" s="16" t="str" cm="1">
         <f t="array" ref="J33" xml:space="preserve"> IF(J$3&lt;&gt;$D33, MID($C33,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K33" s="20" t="str" cm="1">
+      <c r="K33" s="16" t="str" cm="1">
         <f t="array" ref="K33" xml:space="preserve"> IF(K$3&lt;&gt;$D33, MID($C33,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L33" s="20" t="str" cm="1">
+      <c r="L33" s="16" t="str" cm="1">
         <f t="array" ref="L33" xml:space="preserve"> IF(L$3&lt;&gt;$D33, MID($C33,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M33" s="21" t="str" cm="1">
+      <c r="M33" s="17" t="str" cm="1">
         <f t="array" ref="M33" xml:space="preserve"> IF(M$3&lt;&gt;$D33, MID($C33,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C33,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2740,49 +2740,49 @@
       <c r="P33" s="2"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E34" s="20" t="str" cm="1">
+      <c r="E34" s="16" t="str" cm="1">
         <f t="array" ref="E34" xml:space="preserve"> IF(E$3&lt;&gt;$D34, MID($C34,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="F34" s="20" t="str" cm="1">
+      <c r="F34" s="16" t="str" cm="1">
         <f t="array" ref="F34" xml:space="preserve"> IF(F$3&lt;&gt;$D34, MID($C34,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G34" s="20" t="str" cm="1">
+      <c r="G34" s="16" t="str" cm="1">
         <f t="array" ref="G34" xml:space="preserve"> IF(G$3&lt;&gt;$D34, MID($C34,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H34" s="20" t="str" cm="1">
+      <c r="H34" s="16" t="str" cm="1">
         <f t="array" ref="H34" xml:space="preserve"> IF(H$3&lt;&gt;$D34, MID($C34,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="I34" s="20" t="str" cm="1">
+      <c r="I34" s="16" t="str" cm="1">
         <f t="array" ref="I34" xml:space="preserve"> IF(I$3&lt;&gt;$D34, MID($C34,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="J34" s="20" t="str" cm="1">
+      <c r="J34" s="16" t="str" cm="1">
         <f t="array" ref="J34" xml:space="preserve"> IF(J$3&lt;&gt;$D34, MID($C34,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K34" s="20" t="str" cm="1">
+      <c r="K34" s="16" t="str" cm="1">
         <f t="array" ref="K34" xml:space="preserve"> IF(K$3&lt;&gt;$D34, MID($C34,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L34" s="20" t="str" cm="1">
+      <c r="L34" s="16" t="str" cm="1">
         <f t="array" ref="L34" xml:space="preserve"> IF(L$3&lt;&gt;$D34, MID($C34,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M34" s="21" t="str" cm="1">
+      <c r="M34" s="17" t="str" cm="1">
         <f t="array" ref="M34" xml:space="preserve"> IF(M$3&lt;&gt;$D34, MID($C34,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C34,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2790,49 +2790,49 @@
       <c r="P34" s="2"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E35" s="20" t="str" cm="1">
+      <c r="E35" s="16" t="str" cm="1">
         <f t="array" ref="E35" xml:space="preserve"> IF(E$3&lt;&gt;$D35, MID($C35,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>l</v>
       </c>
-      <c r="F35" s="20" t="str" cm="1">
+      <c r="F35" s="16" t="str" cm="1">
         <f t="array" ref="F35" xml:space="preserve"> IF(F$3&lt;&gt;$D35, MID($C35,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G35" s="20" t="str" cm="1">
+      <c r="G35" s="16" t="str" cm="1">
         <f t="array" ref="G35" xml:space="preserve"> IF(G$3&lt;&gt;$D35, MID($C35,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H35" s="20" t="str" cm="1">
+      <c r="H35" s="16" t="str" cm="1">
         <f t="array" ref="H35" xml:space="preserve"> IF(H$3&lt;&gt;$D35, MID($C35,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>\</v>
       </c>
-      <c r="I35" s="20" t="str" cm="1">
+      <c r="I35" s="16" t="str" cm="1">
         <f t="array" ref="I35" xml:space="preserve"> IF(I$3&lt;&gt;$D35, MID($C35,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J35" s="20" t="str" cm="1">
+      <c r="J35" s="16" t="str" cm="1">
         <f t="array" ref="J35" xml:space="preserve"> IF(J$3&lt;&gt;$D35, MID($C35,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K35" s="20" t="str" cm="1">
+      <c r="K35" s="16" t="str" cm="1">
         <f t="array" ref="K35" xml:space="preserve"> IF(K$3&lt;&gt;$D35, MID($C35,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L35" s="20" t="str" cm="1">
+      <c r="L35" s="16" t="str" cm="1">
         <f t="array" ref="L35" xml:space="preserve"> IF(L$3&lt;&gt;$D35, MID($C35,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M35" s="21" t="str" cm="1">
+      <c r="M35" s="17" t="str" cm="1">
         <f t="array" ref="M35" xml:space="preserve"> IF(M$3&lt;&gt;$D35, MID($C35,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C35,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2840,45 +2840,45 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E36" s="20" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G36" s="20" t="str" cm="1">
+      <c r="G36" s="16" t="str" cm="1">
         <f t="array" ref="G36" xml:space="preserve"> IF(G$3&lt;&gt;$D36, MID($C36,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H36" s="20" t="str" cm="1">
+      <c r="H36" s="16" t="str" cm="1">
         <f t="array" ref="H36" xml:space="preserve"> IF(H$3&lt;&gt;$D36, MID($C36,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I36" s="20" t="str" cm="1">
+      <c r="I36" s="16" t="str" cm="1">
         <f t="array" ref="I36" xml:space="preserve"> IF(I$3&lt;&gt;$D36, MID($C36,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J36" s="20" t="str" cm="1">
+      <c r="J36" s="16" t="str" cm="1">
         <f t="array" ref="J36" xml:space="preserve"> IF(J$3&lt;&gt;$D36, MID($C36,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K36" s="20" t="str" cm="1">
+      <c r="K36" s="16" t="str" cm="1">
         <f t="array" ref="K36" xml:space="preserve"> IF(K$3&lt;&gt;$D36, MID($C36,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L36" s="20" t="str" cm="1">
+      <c r="L36" s="16" t="str" cm="1">
         <f t="array" ref="L36" xml:space="preserve"> IF(L$3&lt;&gt;$D36, MID($C36,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M36" s="21" t="str" cm="1">
+      <c r="M36" s="17" t="str" cm="1">
         <f t="array" ref="M36" xml:space="preserve"> IF(M$3&lt;&gt;$D36, MID($C36,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C36,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2886,49 +2886,49 @@
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E37" s="20" t="str" cm="1">
+      <c r="E37" s="16" t="str" cm="1">
         <f t="array" ref="E37" xml:space="preserve"> IF(E$3&lt;&gt;$D37, MID($C37,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>c</v>
       </c>
-      <c r="F37" s="20" t="str" cm="1">
+      <c r="F37" s="16" t="str" cm="1">
         <f t="array" ref="F37" xml:space="preserve"> IF(F$3&lt;&gt;$D37, MID($C37,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G37" s="20" t="str" cm="1">
+      <c r="G37" s="16" t="str" cm="1">
         <f t="array" ref="G37" xml:space="preserve"> IF(G$3&lt;&gt;$D37, MID($C37,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H37" s="20" t="str" cm="1">
+      <c r="H37" s="16" t="str" cm="1">
         <f t="array" ref="H37" xml:space="preserve"> IF(H$3&lt;&gt;$D37, MID($C37,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="I37" s="20" t="str" cm="1">
+      <c r="I37" s="16" t="str" cm="1">
         <f t="array" ref="I37" xml:space="preserve"> IF(I$3&lt;&gt;$D37, MID($C37,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J37" s="20" t="str" cm="1">
+      <c r="J37" s="16" t="str" cm="1">
         <f t="array" ref="J37" xml:space="preserve"> IF(J$3&lt;&gt;$D37, MID($C37,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K37" s="20" t="str" cm="1">
+      <c r="K37" s="16" t="str" cm="1">
         <f t="array" ref="K37" xml:space="preserve"> IF(K$3&lt;&gt;$D37, MID($C37,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L37" s="20" t="str" cm="1">
+      <c r="L37" s="16" t="str" cm="1">
         <f t="array" ref="L37" xml:space="preserve"> IF(L$3&lt;&gt;$D37, MID($C37,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M37" s="21" t="str" cm="1">
+      <c r="M37" s="17" t="str" cm="1">
         <f t="array" ref="M37" xml:space="preserve"> IF(M$3&lt;&gt;$D37, MID($C37,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C37,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2936,49 +2936,49 @@
       <c r="P37" s="2"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E38" s="20" t="str" cm="1">
+      <c r="E38" s="16" t="str" cm="1">
         <f t="array" ref="E38" xml:space="preserve"> IF(E$3&lt;&gt;$D38, MID($C38,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="F38" s="20" t="str" cm="1">
+      <c r="F38" s="16" t="str" cm="1">
         <f t="array" ref="F38" xml:space="preserve"> IF(F$3&lt;&gt;$D38, MID($C38,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G38" s="20" t="str" cm="1">
+      <c r="G38" s="16" t="str" cm="1">
         <f t="array" ref="G38" xml:space="preserve"> IF(G$3&lt;&gt;$D38, MID($C38,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H38" s="20" t="str" cm="1">
+      <c r="H38" s="16" t="str" cm="1">
         <f t="array" ref="H38" xml:space="preserve"> IF(H$3&lt;&gt;$D38, MID($C38,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="I38" s="20" t="str" cm="1">
+      <c r="I38" s="16" t="str" cm="1">
         <f t="array" ref="I38" xml:space="preserve"> IF(I$3&lt;&gt;$D38, MID($C38,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="J38" s="20" t="str" cm="1">
+      <c r="J38" s="16" t="str" cm="1">
         <f t="array" ref="J38" xml:space="preserve"> IF(J$3&lt;&gt;$D38, MID($C38,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K38" s="20" t="str" cm="1">
+      <c r="K38" s="16" t="str" cm="1">
         <f t="array" ref="K38" xml:space="preserve"> IF(K$3&lt;&gt;$D38, MID($C38,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L38" s="20" t="str" cm="1">
+      <c r="L38" s="16" t="str" cm="1">
         <f t="array" ref="L38" xml:space="preserve"> IF(L$3&lt;&gt;$D38, MID($C38,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M38" s="21" t="str" cm="1">
+      <c r="M38" s="17" t="str" cm="1">
         <f t="array" ref="M38" xml:space="preserve"> IF(M$3&lt;&gt;$D38, MID($C38,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C38,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -2986,49 +2986,49 @@
       <c r="P38" s="2"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E39" s="20" t="str" cm="1">
+      <c r="E39" s="16" t="str" cm="1">
         <f t="array" ref="E39" xml:space="preserve"> IF(E$3&lt;&gt;$D39, MID($C39,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="F39" s="20" t="str" cm="1">
+      <c r="F39" s="16" t="str" cm="1">
         <f t="array" ref="F39" xml:space="preserve"> IF(F$3&lt;&gt;$D39, MID($C39,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G39" s="20" t="str" cm="1">
+      <c r="G39" s="16" t="str" cm="1">
         <f t="array" ref="G39" xml:space="preserve"> IF(G$3&lt;&gt;$D39, MID($C39,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="H39" s="20" t="str" cm="1">
+      <c r="H39" s="16" t="str" cm="1">
         <f t="array" ref="H39" xml:space="preserve"> IF(H$3&lt;&gt;$D39, MID($C39,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>[</v>
       </c>
-      <c r="I39" s="20" t="str" cm="1">
+      <c r="I39" s="16" t="str" cm="1">
         <f t="array" ref="I39" xml:space="preserve"> IF(I$3&lt;&gt;$D39, MID($C39,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J39" s="20" t="str" cm="1">
+      <c r="J39" s="16" t="str" cm="1">
         <f t="array" ref="J39" xml:space="preserve"> IF(J$3&lt;&gt;$D39, MID($C39,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K39" s="20" t="str" cm="1">
+      <c r="K39" s="16" t="str" cm="1">
         <f t="array" ref="K39" xml:space="preserve"> IF(K$3&lt;&gt;$D39, MID($C39,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L39" s="20" t="str" cm="1">
+      <c r="L39" s="16" t="str" cm="1">
         <f t="array" ref="L39" xml:space="preserve"> IF(L$3&lt;&gt;$D39, MID($C39,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M39" s="21" t="str" cm="1">
+      <c r="M39" s="17" t="str" cm="1">
         <f t="array" ref="M39" xml:space="preserve"> IF(M$3&lt;&gt;$D39, MID($C39,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C39,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -3036,49 +3036,49 @@
       <c r="P39" s="2"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E40" s="20" t="str" cm="1">
+      <c r="E40" s="16" t="str" cm="1">
         <f t="array" ref="E40" xml:space="preserve"> IF(E$3&lt;&gt;$D40, MID($C40,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="F40" s="20" t="str" cm="1">
+      <c r="F40" s="16" t="str" cm="1">
         <f t="array" ref="F40" xml:space="preserve"> IF(F$3&lt;&gt;$D40, MID($C40,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G40" s="20" t="str" cm="1">
+      <c r="G40" s="16" t="str" cm="1">
         <f t="array" ref="G40" xml:space="preserve"> IF(G$3&lt;&gt;$D40, MID($C40,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H40" s="20" t="str" cm="1">
+      <c r="H40" s="16" t="str" cm="1">
         <f t="array" ref="H40" xml:space="preserve"> IF(H$3&lt;&gt;$D40, MID($C40,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>-</v>
       </c>
-      <c r="I40" s="20" t="str" cm="1">
+      <c r="I40" s="16" t="str" cm="1">
         <f t="array" ref="I40" xml:space="preserve"> IF(I$3&lt;&gt;$D40, MID($C40,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J40" s="20" t="str" cm="1">
+      <c r="J40" s="16" t="str" cm="1">
         <f t="array" ref="J40" xml:space="preserve"> IF(J$3&lt;&gt;$D40, MID($C40,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K40" s="20" t="str" cm="1">
+      <c r="K40" s="16" t="str" cm="1">
         <f t="array" ref="K40" xml:space="preserve"> IF(K$3&lt;&gt;$D40, MID($C40,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L40" s="20" t="str" cm="1">
+      <c r="L40" s="16" t="str" cm="1">
         <f t="array" ref="L40" xml:space="preserve"> IF(L$3&lt;&gt;$D40, MID($C40,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M40" s="21" t="str" cm="1">
+      <c r="M40" s="17" t="str" cm="1">
         <f t="array" ref="M40" xml:space="preserve"> IF(M$3&lt;&gt;$D40, MID($C40,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C40,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -3086,49 +3086,49 @@
       <c r="P40" s="2"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E41" s="20" t="str" cm="1">
+      <c r="E41" s="16" t="str" cm="1">
         <f t="array" ref="E41" xml:space="preserve"> IF(E$3&lt;&gt;$D41, MID($C41,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="F41" s="20" t="str" cm="1">
+      <c r="F41" s="16" t="str" cm="1">
         <f t="array" ref="F41" xml:space="preserve"> IF(F$3&lt;&gt;$D41, MID($C41,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G41" s="20" t="str" cm="1">
+      <c r="G41" s="16" t="str" cm="1">
         <f t="array" ref="G41" xml:space="preserve"> IF(G$3&lt;&gt;$D41, MID($C41,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H41" s="20" t="str" cm="1">
+      <c r="H41" s="16" t="str" cm="1">
         <f t="array" ref="H41" xml:space="preserve"> IF(H$3&lt;&gt;$D41, MID($C41,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="I41" s="20" t="str" cm="1">
+      <c r="I41" s="16" t="str" cm="1">
         <f t="array" ref="I41" xml:space="preserve"> IF(I$3&lt;&gt;$D41, MID($C41,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>]</v>
       </c>
-      <c r="J41" s="20" t="str" cm="1">
+      <c r="J41" s="16" t="str" cm="1">
         <f t="array" ref="J41" xml:space="preserve"> IF(J$3&lt;&gt;$D41, MID($C41,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K41" s="20" t="str" cm="1">
+      <c r="K41" s="16" t="str" cm="1">
         <f t="array" ref="K41" xml:space="preserve"> IF(K$3&lt;&gt;$D41, MID($C41,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L41" s="20" t="str" cm="1">
+      <c r="L41" s="16" t="str" cm="1">
         <f t="array" ref="L41" xml:space="preserve"> IF(L$3&lt;&gt;$D41, MID($C41,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M41" s="21" t="str" cm="1">
+      <c r="M41" s="17" t="str" cm="1">
         <f t="array" ref="M41" xml:space="preserve"> IF(M$3&lt;&gt;$D41, MID($C41,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C41,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -3136,49 +3136,49 @@
       <c r="P41" s="2"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E42" s="20" t="str" cm="1">
+      <c r="E42" s="16" t="str" cm="1">
         <f t="array" ref="E42" xml:space="preserve"> IF(E$3&lt;&gt;$D42, MID($C42,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>b</v>
       </c>
-      <c r="F42" s="20" t="str" cm="1">
+      <c r="F42" s="16" t="str" cm="1">
         <f t="array" ref="F42" xml:space="preserve"> IF(F$3&lt;&gt;$D42, MID($C42,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G42" s="20" t="str" cm="1">
+      <c r="G42" s="16" t="str" cm="1">
         <f t="array" ref="G42" xml:space="preserve"> IF(G$3&lt;&gt;$D42, MID($C42,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H42" s="20" t="str" cm="1">
+      <c r="H42" s="16" t="str" cm="1">
         <f t="array" ref="H42" xml:space="preserve"> IF(H$3&lt;&gt;$D42, MID($C42,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>/</v>
       </c>
-      <c r="I42" s="20" t="str" cm="1">
+      <c r="I42" s="16" t="str" cm="1">
         <f t="array" ref="I42" xml:space="preserve"> IF(I$3&lt;&gt;$D42, MID($C42,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J42" s="20" t="str" cm="1">
+      <c r="J42" s="16" t="str" cm="1">
         <f t="array" ref="J42" xml:space="preserve"> IF(J$3&lt;&gt;$D42, MID($C42,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K42" s="20" t="str" cm="1">
+      <c r="K42" s="16" t="str" cm="1">
         <f t="array" ref="K42" xml:space="preserve"> IF(K$3&lt;&gt;$D42, MID($C42,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L42" s="20" t="str" cm="1">
+      <c r="L42" s="16" t="str" cm="1">
         <f t="array" ref="L42" xml:space="preserve"> IF(L$3&lt;&gt;$D42, MID($C42,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M42" s="21" t="str" cm="1">
+      <c r="M42" s="17" t="str" cm="1">
         <f t="array" ref="M42" xml:space="preserve"> IF(M$3&lt;&gt;$D42, MID($C42,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C42,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -3186,49 +3186,49 @@
       <c r="P42" s="2"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E43" s="20" t="str" cm="1">
+      <c r="E43" s="16" t="str" cm="1">
         <f t="array" ref="E43" xml:space="preserve"> IF(E$3&lt;&gt;$D43, MID($C43,E$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,E$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="F43" s="20" t="str" cm="1">
+      <c r="F43" s="16" t="str" cm="1">
         <f t="array" ref="F43" xml:space="preserve"> IF(F$3&lt;&gt;$D43, MID($C43,F$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,F$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G43" s="20" t="str" cm="1">
+      <c r="G43" s="16" t="str" cm="1">
         <f t="array" ref="G43" xml:space="preserve"> IF(G$3&lt;&gt;$D43, MID($C43,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H43" s="20" t="str" cm="1">
+      <c r="H43" s="16" t="str" cm="1">
         <f t="array" ref="H43" xml:space="preserve"> IF(H$3&lt;&gt;$D43, MID($C43,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I43" s="20" t="str" cm="1">
+      <c r="I43" s="16" t="str" cm="1">
         <f t="array" ref="I43" xml:space="preserve"> IF(I$3&lt;&gt;$D43, MID($C43,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v>;</v>
       </c>
-      <c r="J43" s="20" t="str" cm="1">
+      <c r="J43" s="16" t="str" cm="1">
         <f t="array" ref="J43" xml:space="preserve"> IF(J$3&lt;&gt;$D43, MID($C43,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K43" s="20" t="str" cm="1">
+      <c r="K43" s="16" t="str" cm="1">
         <f t="array" ref="K43" xml:space="preserve"> IF(K$3&lt;&gt;$D43, MID($C43,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L43" s="20" t="str" cm="1">
+      <c r="L43" s="16" t="str" cm="1">
         <f t="array" ref="L43" xml:space="preserve"> IF(L$3&lt;&gt;$D43, MID($C43,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M43" s="21" t="str" cm="1">
+      <c r="M43" s="17" t="str" cm="1">
         <f t="array" ref="M43" xml:space="preserve"> IF(M$3&lt;&gt;$D43, MID($C43,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C43,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
@@ -3236,45 +3236,45 @@
       <c r="P43" s="2"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E44" s="20" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G44" s="20" t="str" cm="1">
+      <c r="G44" s="16" t="str" cm="1">
         <f t="array" ref="G44" xml:space="preserve"> IF(G$3&lt;&gt;$D44, MID($C44,G$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,G$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H44" s="20" t="str" cm="1">
+      <c r="H44" s="16" t="str" cm="1">
         <f t="array" ref="H44" xml:space="preserve"> IF(H$3&lt;&gt;$D44, MID($C44,H$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,H$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I44" s="20" t="str" cm="1">
+      <c r="I44" s="16" t="str" cm="1">
         <f t="array" ref="I44" xml:space="preserve"> IF(I$3&lt;&gt;$D44, MID($C44,I$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,I$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J44" s="20" t="str" cm="1">
+      <c r="J44" s="16" t="str" cm="1">
         <f t="array" ref="J44" xml:space="preserve"> IF(J$3&lt;&gt;$D44, MID($C44,J$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,J$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K44" s="20" t="str" cm="1">
+      <c r="K44" s="16" t="str" cm="1">
         <f t="array" ref="K44" xml:space="preserve"> IF(K$3&lt;&gt;$D44, MID($C44,K$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,K$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L44" s="20" t="str" cm="1">
+      <c r="L44" s="16" t="str" cm="1">
         <f t="array" ref="L44" xml:space="preserve"> IF(L$3&lt;&gt;$D44, MID($C44,L$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,L$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M44" s="21" t="str" cm="1">
+      <c r="M44" s="17" t="str" cm="1">
         <f t="array" ref="M44" xml:space="preserve"> IF(M$3&lt;&gt;$D44, MID($C44,M$3,1), INDEX(音調表!$D$3:$D$12, MATCH(TRUE, EXACT(MID($C44,M$3,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
